--- a/products-storage/14-peredacha-id-pod-podpis/03-opis-peredavaemogo-komplekta.xlsx
+++ b/products-storage/14-peredacha-id-pod-podpis/03-opis-peredavaemogo-komplekta.xlsx
@@ -649,7 +649,7 @@
     <row r="2" ht="96" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Прочитайте до того, как заполнять. Это типовой рабочий документ, а не юридическая консультация. Он не обещает, что комплект примут с первого раза: часть замечаний приходит независимо от того, как он собран и передан. Что он делает — фиксирует состав передачи: что именно, в каком объёме и в скольких экземплярах ушло второй стороне. Тексты комплекта вычитку юристом не проходили. Приоритет всегда у вашего договора: состав документации, форма и адресат передачи, срок рассмотрения определяются им, а обязательные требования к формам вы проверяете сами в действующей редакции на дату передачи. Сроков и норм числом в файле нет намеренно: они меняются, а скачанный файл не обновляется.</t>
+          <t>Прочитайте до того, как заполнять. Это типовой рабочий документ, а не юридическая консультация. Он не обещает, что комплект примут с первого раза: часть замечаний приходит независимо от того, как он собран и передан. Что он делает — фиксирует состав передачи: что именно, в каком объёме и в скольких экземплярах ушло второй стороне. Тексты прошли вычитку юристом в типовой редакции. Нормативная сверка форм и порядка передачи не проводилась, и вычитка её не заменяет. Приоритет всегда у вашего договора: состав документации, форма и адресат передачи, срок рассмотрения определяются им, а обязательные требования к формам вы проверяете сами в действующей редакции на дату передачи. Сроков и норм числом в файле нет намеренно: они меняются, а скачанный файл не обновляется.</t>
         </is>
       </c>
     </row>
